--- a/Dipseva_Ledger_NEW.xlsx
+++ b/Dipseva_Ledger_NEW.xlsx
@@ -26928,7 +26928,7 @@
           <t>Anand Bansode</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Caterers</t>
